--- a/analysis/开发人维度/张子轩_sku_report.xlsx
+++ b/analysis/开发人维度/张子轩_sku_report.xlsx
@@ -1004,12 +1004,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>B0GJSCJ4MQ</t>
+          <t>B0GJSR9W3D</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2640006</t>
+          <t>2640009</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1018,13 +1018,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E2" t="n">
-        <v>51.53</v>
+        <v>88.67</v>
       </c>
       <c r="F2" t="n">
-        <v>-22.11</v>
+        <v>-5.59</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -1038,46 +1038,46 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>B0GJSCPDMM</t>
+          <t>B0GK6HSKGN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2640008</t>
+          <t>2640023</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>AM-Xfengjun-UK</t>
+          <t>AM-Chaiqing-UK</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>433.26</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>96.69</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>欧洲精铺2025</t>
+          <t>欧洲精铺2025,欧洲精铺2025非标品</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>B0GJSR9W3D</t>
+          <t>B0GJSCPDMM</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2640009</t>
+          <t>2640008</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1086,50 +1086,50 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>62</v>
       </c>
       <c r="E4" t="n">
-        <v>88.67</v>
+        <v>433.26</v>
       </c>
       <c r="F4" t="n">
-        <v>-5.59</v>
+        <v>96.69</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>欧洲精铺2025,绿标</t>
+          <t>欧洲精铺2025</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>B0GJYPHVG3</t>
+          <t>B0GJS8PQ9P</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2640013</t>
+          <t>2640004</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AM-Xfengjun-UK</t>
+          <t>AM-Chaiqing-UK</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>103.8</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>13.28</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -1140,30 +1140,30 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>B0GJS8PQ9P</t>
+          <t>B0GJYPHVG3</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2640004</t>
+          <t>2640013</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AM-Chaiqing-UK</t>
+          <t>AM-Xfengjun-UK</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>103.8</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>13.28</v>
       </c>
       <c r="G6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -1174,12 +1174,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>B0GKN58FPT</t>
+          <t>B0GJSCJ4MQ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2640024</t>
+          <t>2640006</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1188,54 +1188,54 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E7" t="n">
-        <v>91.17</v>
+        <v>51.53</v>
       </c>
       <c r="F7" t="n">
-        <v>-14.48</v>
+        <v>-22.11</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>欧洲精铺2025,欧洲精铺2025非标品,绿标</t>
+          <t>欧洲精铺2025,绿标</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>B0GK6HSKGN</t>
+          <t>B0GJSR6M9Y</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2640023</t>
+          <t>2640010</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AM-Chaiqing-UK</t>
+          <t>AM-Xfengjun-UK</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>45.72</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>-12.29</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>欧洲精铺2025,欧洲精铺2025非标品</t>
+          <t>欧洲精铺2025</t>
         </is>
       </c>
     </row>
@@ -1276,12 +1276,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>B0GJSR6M9Y</t>
+          <t>B0GKN58FPT</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2640010</t>
+          <t>2640024</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1290,20 +1290,20 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E10" t="n">
-        <v>45.72</v>
+        <v>91.17</v>
       </c>
       <c r="F10" t="n">
-        <v>-12.29</v>
+        <v>-14.48</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>欧洲精铺2025</t>
+          <t>欧洲精铺2025,欧洲精铺2025非标品,绿标</t>
         </is>
       </c>
     </row>
@@ -1400,12 +1400,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>B0GK6S851C</t>
+          <t>B0GL1H1L3Q</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2640022</t>
+          <t>2640026</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1414,16 +1414,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="E2" t="n">
-        <v>360.11</v>
+        <v>46.32</v>
       </c>
       <c r="F2" t="n">
-        <v>94.27</v>
+        <v>-1.27</v>
       </c>
       <c r="G2" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -1434,30 +1434,30 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>B0GL1H1L3Q</t>
+          <t>B0GL64HL5S</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2640026</t>
+          <t>2640028</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>AM-Yehao-UK</t>
+          <t>AM-Xfengjun-UK</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>46.32</v>
+        <v>19.34</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.27</v>
+        <v>1.75</v>
       </c>
       <c r="G3" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -1468,30 +1468,30 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>B0GL64HL5S</t>
+          <t>B0GK6S851C</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2640028</t>
+          <t>2640022</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AM-Xfengjun-UK</t>
+          <t>AM-Yehao-UK</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>45</v>
       </c>
       <c r="E4" t="n">
-        <v>19.34</v>
+        <v>360.11</v>
       </c>
       <c r="F4" t="n">
-        <v>1.75</v>
+        <v>94.27</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -1558,12 +1558,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>B0GR43F89Y</t>
+          <t>B0GR4B1QSH</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2640034</t>
+          <t>2640037</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1572,16 +1572,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>52.3</v>
+        <v>23.96</v>
       </c>
       <c r="F2" t="n">
-        <v>-23.76</v>
+        <v>-8.289999999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -1592,30 +1592,30 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>B0GR88QNGV</t>
+          <t>B0GQSQ8D4S</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2640051</t>
+          <t>2640038</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>AM-GC-UK</t>
+          <t>AM-Pyongqian-UK</t>
         </is>
       </c>
       <c r="D3" t="n">
+        <v>8</v>
+      </c>
+      <c r="E3" t="n">
+        <v>60.09</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="G3" t="n">
         <v>3</v>
-      </c>
-      <c r="E3" t="n">
-        <v>20.94</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="G3" t="n">
-        <v>11</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -1626,98 +1626,98 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>B0GR4B1QSH</t>
+          <t>B0GR88QNGV</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2640037</t>
+          <t>2640051</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AM-Xfengjun-UK</t>
+          <t>AM-GC-UK</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>23.96</v>
+        <v>20.94</v>
       </c>
       <c r="F4" t="n">
-        <v>-8.289999999999999</v>
+        <v>0.59</v>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>欧洲精铺2025,欧洲精铺2025非标品,绿标</t>
+          <t>欧洲精铺2025,欧洲精铺2025非标品</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>B0GQSW8FRV</t>
+          <t>B0GR43F89Y</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2640033</t>
+          <t>2640034</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AM-Liuhu-UK</t>
+          <t>AM-Xfengjun-UK</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E5" t="n">
-        <v>93.17</v>
+        <v>52.3</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.02</v>
+        <v>-23.76</v>
       </c>
       <c r="G5" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>欧洲精铺2025,欧洲精铺2025非标品</t>
+          <t>欧洲精铺2025,欧洲精铺2025非标品,绿标</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>B0GR9QX2BB</t>
+          <t>B0GRGP3BJ1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2640056</t>
+          <t>2640054</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AM-GC-UK</t>
+          <t>AM-Xfengjun-UK</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>9.960000000000001</v>
+        <v>9.58</v>
       </c>
       <c r="F6" t="n">
-        <v>1.53</v>
+        <v>-1.75</v>
       </c>
       <c r="G6" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -1762,12 +1762,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>B0GR3TXB45</t>
+          <t>B0GR5J3HDM</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2640030</t>
+          <t>2640046</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1776,50 +1776,50 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>39.88</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>-8.48</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>欧洲精铺2025,欧洲精铺2025非标品,绿标</t>
+          <t>欧洲精铺2025,欧洲精铺2025非标品</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>B0GQSQ8D4S</t>
+          <t>B0GQSFWBJ9</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2640038</t>
+          <t>2640029</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AM-Pyongqian-UK</t>
+          <t>AM-Liuhu-UK</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E9" t="n">
-        <v>60.09</v>
+        <v>34.93</v>
       </c>
       <c r="F9" t="n">
-        <v>1.89</v>
+        <v>-6.45</v>
       </c>
       <c r="G9" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1830,46 +1830,46 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>B0GQSFWBJ9</t>
+          <t>B0GL24G51C</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2640029</t>
+          <t>2640027</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>AM-Liuhu-UK</t>
+          <t>AM-GC-UK</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E10" t="n">
-        <v>34.93</v>
+        <v>47.97</v>
       </c>
       <c r="F10" t="n">
-        <v>-6.45</v>
+        <v>4.26</v>
       </c>
       <c r="G10" t="n">
         <v>11</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>欧洲精铺2025,欧洲精铺2025非标品</t>
+          <t>欧洲精铺2025</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>B0GR46R9FV</t>
+          <t>B0GR3TXB45</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2640040</t>
+          <t>2640030</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1878,13 +1878,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E11" t="n">
-        <v>17.56</v>
+        <v>39.88</v>
       </c>
       <c r="F11" t="n">
-        <v>-8.52</v>
+        <v>-8.48</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -1932,12 +1932,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>B0GQSHYP4L</t>
+          <t>B0GQSW8FRV</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2640036</t>
+          <t>2640033</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1946,16 +1946,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>65</v>
+        <v>13</v>
       </c>
       <c r="E13" t="n">
-        <v>483.09</v>
+        <v>93.17</v>
       </c>
       <c r="F13" t="n">
-        <v>142.83</v>
+        <v>-2.02</v>
       </c>
       <c r="G13" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1966,30 +1966,30 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>B0GRGDWR42</t>
+          <t>B0GR9QX2BB</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2640055</t>
+          <t>2640056</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>AM-Yangbo-UK</t>
+          <t>AM-GC-UK</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E14" t="n">
-        <v>76.38</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>6.51</v>
+        <v>1.53</v>
       </c>
       <c r="G14" t="n">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -2000,12 +2000,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>B0GL24G51C</t>
+          <t>B0GK5SFMLQ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2640027</t>
+          <t>2640021</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2014,16 +2014,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="E15" t="n">
-        <v>47.97</v>
+        <v>338.42</v>
       </c>
       <c r="F15" t="n">
-        <v>4.26</v>
+        <v>35.16</v>
       </c>
       <c r="G15" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -2034,132 +2034,132 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>B0GQXR19SQ</t>
+          <t>B0GRGX2X2N</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2640041</t>
+          <t>2640053</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>AM-Pyongqian-UK</t>
+          <t>AM-Liuhu-UK</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="E16" t="n">
-        <v>67.84999999999999</v>
+        <v>271.66</v>
       </c>
       <c r="F16" t="n">
-        <v>-11.42</v>
+        <v>71.73</v>
       </c>
       <c r="G16" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>欧洲精铺2025,欧洲精铺2025非标品</t>
+          <t>欧洲精铺2025</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>B0GRGX2X2N</t>
+          <t>B0GR46R9FV</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2640053</t>
+          <t>2640040</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>AM-Liuhu-UK</t>
+          <t>AM-Xfengjun-UK</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>34</v>
+        <v>3</v>
       </c>
       <c r="E17" t="n">
-        <v>271.66</v>
+        <v>17.56</v>
       </c>
       <c r="F17" t="n">
-        <v>71.73</v>
+        <v>-8.52</v>
       </c>
       <c r="G17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>欧洲精铺2025</t>
+          <t>欧洲精铺2025,欧洲精铺2025非标品,绿标</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>B0GK5SFMLQ</t>
+          <t>B0GQXR19SQ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2640021</t>
+          <t>2640041</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AM-GC-UK</t>
+          <t>AM-Pyongqian-UK</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="E18" t="n">
-        <v>338.42</v>
+        <v>67.84999999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>35.16</v>
+        <v>-11.42</v>
       </c>
       <c r="G18" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>欧洲精铺2025</t>
+          <t>欧洲精铺2025,欧洲精铺2025非标品</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>B0GR5J3HDM</t>
+          <t>B0GQSQVZT8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2640046</t>
+          <t>2640035</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AM-Xfengjun-UK</t>
+          <t>AM-Pyongqian-UK</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>35.95</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -2170,102 +2170,102 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>B0GRGP3BJ1</t>
+          <t>B0GQSHYP4L</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2640054</t>
+          <t>2640036</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AM-Xfengjun-UK</t>
+          <t>AM-Liuhu-UK</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>65</v>
       </c>
       <c r="E20" t="n">
-        <v>9.58</v>
+        <v>483.09</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.75</v>
+        <v>142.83</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>欧洲精铺2025</t>
+          <t>欧洲精铺2025,欧洲精铺2025非标品</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>B0GQSQVZT8</t>
+          <t>B0GRGMPCR5</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2640035</t>
+          <t>2640049</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AM-Pyongqian-UK</t>
+          <t>AM-Xfengjun-UK</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>4</v>
       </c>
       <c r="E21" t="n">
-        <v>35.95</v>
+        <v>23.96</v>
       </c>
       <c r="F21" t="n">
-        <v>1.34</v>
+        <v>-3.12</v>
       </c>
       <c r="G21" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>欧洲精铺2025,欧洲精铺2025非标品</t>
+          <t>欧洲精铺2025,欧洲精铺2025非标品,绿标</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>B0GRGMPCR5</t>
+          <t>B0GRGDWR42</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2640049</t>
+          <t>2640055</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AM-Xfengjun-UK</t>
+          <t>AM-Yangbo-UK</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E22" t="n">
-        <v>23.96</v>
+        <v>76.38</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.12</v>
+        <v>6.51</v>
       </c>
       <c r="G22" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>欧洲精铺2025,欧洲精铺2025非标品,绿标</t>
+          <t>欧洲精铺2025</t>
         </is>
       </c>
     </row>
@@ -2328,46 +2328,46 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>B0GXYTD1F6</t>
+          <t>B0GXV3WCVX</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2640081</t>
+          <t>2640068</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>AM-Yulu-UK</t>
+          <t>AM-Xfengjun-UK</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>7.99</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>欧洲精铺2025,欧洲精铺2025非标品</t>
+          <t>欧洲精铺2025</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>B0GZ3N2X8F</t>
+          <t>B0GYQRDNY9</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2640103</t>
+          <t>2640091</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -2382,10 +2382,10 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.3</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -2396,30 +2396,30 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>B0GY8562ZQ</t>
+          <t>B0GXVYSM16</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2640089</t>
+          <t>2640067</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AM-Tyulian-DE</t>
+          <t>AM-Yulu-UK</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>54.92</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>18.18</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -2430,17 +2430,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>B0GYWWQX3M</t>
+          <t>B0GXVGZ5W9</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2640097</t>
+          <t>2640080</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AM-Yulu-UK</t>
+          <t>AM-Yujinbing-UK</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -2450,26 +2450,26 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>-0.52</v>
       </c>
       <c r="G5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>欧洲精铺2025</t>
+          <t>欧洲精铺2025,欧洲精铺2025非标品</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>B0GZ39ZRJJ</t>
+          <t>B0GX1DCCPQ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2640104</t>
+          <t>2640065</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2478,16 +2478,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>29.95</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.21</v>
+        <v>-15.44</v>
       </c>
       <c r="G6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -2498,30 +2498,30 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>B0GYNDHZ5S</t>
+          <t>B0GYDC96YV</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2640087</t>
+          <t>2640083</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>AM-Yangbo-UK</t>
+          <t>AM-Yulu-UK</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>7.58</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>-2.25</v>
       </c>
       <c r="G7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -2532,80 +2532,80 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>B0GY7YZF5T</t>
+          <t>B0GXVNF61M</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2640087</t>
+          <t>2640069</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AM-Tyulian-DE</t>
+          <t>AM-Yulu-UK</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E8" t="n">
-        <v>20.43</v>
+        <v>39.06</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.48</v>
+        <v>-11.37</v>
       </c>
       <c r="G8" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>欧洲精铺2025,欧洲精铺2025非标品</t>
+          <t>欧洲精铺2025</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>B0GXV3WCVX</t>
+          <t>B0GY7YZF5T</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2640068</t>
+          <t>2640087</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AM-Xfengjun-UK</t>
+          <t>AM-Tyulian-DE</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>20.43</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>-0.48</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>欧洲精铺2025</t>
+          <t>欧洲精铺2025,欧洲精铺2025非标品</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>B0GYMS83BF</t>
+          <t>B0GYMZYR8S</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2640085</t>
+          <t>2640084</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2614,16 +2614,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>7.99</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.45</v>
+        <v>2.77</v>
       </c>
       <c r="G10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -2634,17 +2634,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>B0GRGFGV4Y</t>
+          <t>B0GZ3N2X8F</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2640057</t>
+          <t>2640103</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AM-Pyongqian-UK</t>
+          <t>AM-Tyulian-UK</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -2654,10 +2654,10 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.83</v>
+        <v>-0.3</v>
       </c>
       <c r="G11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -2668,51 +2668,51 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>B0GYN4D2JJ</t>
+          <t>B0GX1Q7T2T</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2640090</t>
+          <t>2640062</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>AM-Yangbo-UK</t>
+          <t>AM-Yujinbing-UK</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>17.96</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>-2.17</v>
       </c>
       <c r="G12" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>欧洲精铺2025,欧洲精铺2025非标品</t>
+          <t>欧洲精铺2025</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>B0GYDVKL5S</t>
+          <t>B0GYN4D2JJ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2640088</t>
+          <t>2640090</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AM-Yulu-UK</t>
+          <t>AM-Yangbo-UK</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -2725,7 +2725,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -2736,12 +2736,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>B0GYWLZV8M</t>
+          <t>B0GYDVKL5S</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2640099</t>
+          <t>2640088</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2750,50 +2750,50 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>29.57</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.67</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>欧洲精铺2025</t>
+          <t>欧洲精铺2025,欧洲精铺2025非标品</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>B0GYMZYR8S</t>
+          <t>B0GYR68DCM</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2640084</t>
+          <t>2640030</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>AM-Yujinbing-UK</t>
+          <t>AM-Tyulian-UK</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>7.99</v>
+        <v>5.99</v>
       </c>
       <c r="F15" t="n">
-        <v>2.77</v>
+        <v>-1.67</v>
       </c>
       <c r="G15" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -2804,12 +2804,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>B0GXVYSM16</t>
+          <t>B0GYWWQX3M</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2640067</t>
+          <t>2640097</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2818,16 +2818,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>54.92</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>18.18</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -2838,17 +2838,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>B0GX1PTS8L</t>
+          <t>B0GRGFGV4Y</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2640066</t>
+          <t>2640057</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>AM-Yujinbing-UK</t>
+          <t>AM-Pyongqian-UK</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -2858,7 +2858,7 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>-2.83</v>
       </c>
       <c r="G17" t="n">
         <v>15</v>
@@ -2872,64 +2872,64 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>B0GXV6L3Q2</t>
+          <t>B0GYR72DB3</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2640082</t>
+          <t>2640096</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AM-Yujinbing-UK</t>
+          <t>AM-Liuhu-UK</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>112.27</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.72</v>
+        <v>-9.390000000000001</v>
       </c>
       <c r="G18" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>欧洲精铺2025,欧洲精铺2025非标品</t>
+          <t>欧洲精铺2025</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>B0GXVNF61M</t>
+          <t>B0GX1PTS8L</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2640069</t>
+          <t>2640066</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AM-Yulu-UK</t>
+          <t>AM-Yujinbing-UK</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>39.06</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>-11.37</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -2940,132 +2940,132 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>B0GYDC96YV</t>
+          <t>B0GZ39ZRJJ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2640083</t>
+          <t>2640104</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AM-Yulu-UK</t>
+          <t>AM-Yujinbing-UK</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>7.58</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.25</v>
+        <v>-0.21</v>
       </c>
       <c r="G20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>欧洲精铺2025,欧洲精铺2025非标品</t>
+          <t>欧洲精铺2025</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>B0GYQRDNY9</t>
+          <t>B0GYDHT2GY</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2640091</t>
+          <t>2640086</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AM-Tyulian-UK</t>
+          <t>AM-Yulu-UK</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>15.98</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>-1.71</v>
       </c>
       <c r="G21" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>欧洲精铺2025</t>
+          <t>欧洲精铺2025,欧洲精铺2025非标品</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>B0GYR68DCM</t>
+          <t>B0GYWLZV8M</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2640030</t>
+          <t>2640099</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AM-Tyulian-UK</t>
+          <t>AM-Yulu-UK</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E22" t="n">
-        <v>5.99</v>
+        <v>29.57</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.67</v>
+        <v>-3.67</v>
       </c>
       <c r="G22" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>欧洲精铺2025,欧洲精铺2025非标品</t>
+          <t>欧洲精铺2025</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>B0GYDHT2GY</t>
+          <t>B0GYMS83BF</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2640086</t>
+          <t>2640085</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AM-Yulu-UK</t>
+          <t>AM-Yujinbing-UK</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>15.98</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.71</v>
+        <v>-1.45</v>
       </c>
       <c r="G23" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -3076,27 +3076,27 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>B0GXVGZ5W9</t>
+          <t>B0GXYTD1F6</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2640080</t>
+          <t>2640081</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AM-Yujinbing-UK</t>
+          <t>AM-Yulu-UK</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>7.99</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.52</v>
+        <v>1.55</v>
       </c>
       <c r="G24" t="n">
         <v>14</v>
@@ -3110,46 +3110,46 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>B0GX1DCCPQ</t>
+          <t>B0GYNDHZ5S</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2640065</t>
+          <t>2640087</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AM-Yujinbing-UK</t>
+          <t>AM-Yangbo-UK</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>29.95</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>-15.44</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>欧洲精铺2025</t>
+          <t>欧洲精铺2025,欧洲精铺2025非标品</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>B0GX1Q7T2T</t>
+          <t>B0GXV6L3Q2</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2640062</t>
+          <t>2640082</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3158,37 +3158,37 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>17.96</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.17</v>
+        <v>-0.72</v>
       </c>
       <c r="G26" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>欧洲精铺2025</t>
+          <t>欧洲精铺2025,欧洲精铺2025非标品</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>B0GZ3QBM9C</t>
+          <t>B0GY8562ZQ</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2640106</t>
+          <t>2640089</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>AM-Yujinbing-UK</t>
+          <t>AM-Tyulian-DE</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -3201,7 +3201,7 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -3212,30 +3212,30 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>B0GYR72DB3</t>
+          <t>B0GZ3QBM9C</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2640096</t>
+          <t>2640106</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>AM-Liuhu-UK</t>
+          <t>AM-Yujinbing-UK</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>112.27</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>-9.390000000000001</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -3302,17 +3302,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>B0H2Z1P7RK</t>
+          <t>B0H3BHR6VM</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2640202</t>
+          <t>2640228</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>AM-Yulu-UK</t>
+          <t>AM-Yujinbing-UK</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -3336,17 +3336,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>B0H2DJKK31</t>
+          <t>B0H2W1SMG7</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2640167</t>
+          <t>2640203</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>AM-Yujinbing-UK</t>
+          <t>AM-Yehao-UK</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -3370,17 +3370,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>B0H1C4D94Z</t>
+          <t>B0H2527THP</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2640138</t>
+          <t>2640161</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AM-Tyulian-UK</t>
+          <t>AM-Tyulian-DE</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -3393,7 +3393,7 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -3404,17 +3404,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>B0H2YF6VXT</t>
+          <t>B0GZNMPNPV</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2640197</t>
+          <t>2640101</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AM-Tyulian-UK</t>
+          <t>AM-Yulu-UK</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -3427,7 +3427,7 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -3438,17 +3438,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>B0H33TQDHQ</t>
+          <t>B0H2Z1P7RK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2640208</t>
+          <t>2640202</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AM-Liuhu-UK</t>
+          <t>AM-Yulu-UK</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -3472,17 +3472,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>B0H3397MB8</t>
+          <t>B0GZMCGMK2</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2640210</t>
+          <t>2640105</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>AM-Liuhu-UK</t>
+          <t>AM-Yehao-UK</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -3495,7 +3495,7 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -3506,12 +3506,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>B0H35FT9Z7</t>
+          <t>B0H33RR3Z3</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2640219</t>
+          <t>2640215</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3540,17 +3540,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>B0H2YZSJKX</t>
+          <t>B0H1C4D94Z</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2640175</t>
+          <t>2640138</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AM-Yulu-UK</t>
+          <t>AM-Tyulian-UK</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -3563,7 +3563,7 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -3574,17 +3574,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>B0H2YGWGW5</t>
+          <t>B0H3BCPZGV</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2640207</t>
+          <t>2640221</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>AM-Tyulian-UK</t>
+          <t>AM-Yujinbing-UK</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -3608,17 +3608,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>B0GZNTWZHF</t>
+          <t>B0H2YF6VXT</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2640108</t>
+          <t>2640197</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AM-Yulu-UK</t>
+          <t>AM-Tyulian-UK</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -3631,7 +3631,7 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -3642,17 +3642,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>B0H29TRBYQ</t>
+          <t>B0H2YY4F3H</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2640166</t>
+          <t>2640187</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>AM-Tyulian-UK</t>
+          <t>AM-Yulu-UK</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -3676,12 +3676,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>B0H33RR3Z3</t>
+          <t>B0GZNTWZHF</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2640215</t>
+          <t>2640108</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -3699,7 +3699,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -3710,12 +3710,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>B0H2YY4F3H</t>
+          <t>B0H2DM9C65</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2640187</t>
+          <t>2640164</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -3744,17 +3744,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>B0H339PWY8</t>
+          <t>B0H35J5QL3</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2640154</t>
+          <t>2640218</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>AM-Liuhu-UK</t>
+          <t>AM-Yulu-UK</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -3778,17 +3778,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>B0H2W1SMG7</t>
+          <t>B0H339PWY8</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2640203</t>
+          <t>2640154</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>AM-Yehao-UK</t>
+          <t>AM-Liuhu-UK</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -3812,17 +3812,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>B0GZMHDZ7F</t>
+          <t>B0H1BQ7MXZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2640106</t>
+          <t>2640068</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>AM-Tyulian-DE</t>
+          <t>AM-Tyulian-UK</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -3832,10 +3832,10 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.17</v>
+        <v>-0.63</v>
       </c>
       <c r="G17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -3846,17 +3846,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>B0H1GQQG1C</t>
+          <t>B0H2YFJ9DL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2640137</t>
+          <t>2640193</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AM-Yehao-UK</t>
+          <t>AM-Tyulian-UK</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -3869,7 +3869,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -3880,17 +3880,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>B0H3BHR6VM</t>
+          <t>B0GZNM54XT</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2640228</t>
+          <t>2640107</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AM-Yujinbing-UK</t>
+          <t>AM-Yulu-UK</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -3903,7 +3903,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -3914,12 +3914,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>B0H2527THP</t>
+          <t>B0H394PDJ7</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2640161</t>
+          <t>2640222</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3948,17 +3948,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>B0H14X43H3</t>
+          <t>B0H14SC4QH</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2640008</t>
+          <t>2640120</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AM-Tyulian-UK</t>
+          <t>AM-Yehao-UK</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -3971,7 +3971,7 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -3982,12 +3982,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>B0H2DM9C65</t>
+          <t>B0H2YW1PZB</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2640164</t>
+          <t>2640181</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -4016,17 +4016,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>B0GZNS6RBN</t>
+          <t>B0H14X43H3</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2640100</t>
+          <t>2640008</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AM-Yulu-UK</t>
+          <t>AM-Tyulian-UK</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -4039,7 +4039,7 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -4050,17 +4050,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>B0H1WB5NTJ</t>
+          <t>B0H2Y1QLG1</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2640146</t>
+          <t>2640194</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AM-Yulu-UK</t>
+          <t>AM-Tyulian-UK</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -4084,12 +4084,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>B0H35J5QL3</t>
+          <t>B0H2Z19MY2</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2640218</t>
+          <t>2640195</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -4118,12 +4118,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>B0H2DL1GKC</t>
+          <t>B0H11M6BHL</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2640168</t>
+          <t>2640127</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -4152,17 +4152,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>B0H2DQ4FQB</t>
+          <t>B0H1WHLRJN</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2640172</t>
+          <t>2640151</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>AM-Yujinbing-UK</t>
+          <t>AM-shangchi-UK</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -4186,12 +4186,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>B0H2Z19MY2</t>
+          <t>B0H1CXXQRB</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2640195</t>
+          <t>2640117</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4220,17 +4220,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>B0H2YFJ9DL</t>
+          <t>B0H1W6487R</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2640193</t>
+          <t>2640142</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>AM-Tyulian-UK</t>
+          <t>AM-Liuhu-UK</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -4254,12 +4254,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>B0H394PDJ7</t>
+          <t>B0H1CRQG45</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2640222</t>
+          <t>2640131</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4288,17 +4288,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>B0H2YJKM8P</t>
+          <t>B0H2V9HTQP</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2640205</t>
+          <t>2640196</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>AM-Tyulian-UK</t>
+          <t>AM-shangchi-UK</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -4322,17 +4322,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>B0H1GLLCFJ</t>
+          <t>B0H2YZSJKX</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2640133</t>
+          <t>2640175</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>AM-Liuhu-UK</t>
+          <t>AM-Yulu-UK</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -4356,17 +4356,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>B0H2YTV3BQ</t>
+          <t>B0H29TRBYQ</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2640189</t>
+          <t>2640166</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>AM-Yulu-UK</t>
+          <t>AM-Tyulian-UK</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -4390,12 +4390,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>B0H2VTJZVG</t>
+          <t>B0H1GQQG1C</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2640198</t>
+          <t>2640137</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4413,7 +4413,7 @@
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -4424,17 +4424,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>B0H33DBPRM</t>
+          <t>B0H14K2HHF</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2640178</t>
+          <t>2640123</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>AM-Liuhu-UK</t>
+          <t>AM-Tyulian-UK</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -4447,7 +4447,7 @@
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -4458,17 +4458,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>B0H14SC4QH</t>
+          <t>B0H24VSSGX</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2640120</t>
+          <t>2640158</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>AM-Yehao-UK</t>
+          <t>AM-Tyulian-DE</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -4492,17 +4492,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>B0GZMCGMK2</t>
+          <t>B0H3397MB8</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2640105</t>
+          <t>2640210</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>AM-Yehao-UK</t>
+          <t>AM-Liuhu-UK</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -4515,7 +4515,7 @@
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -4526,17 +4526,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>B0H1BQ7MXZ</t>
+          <t>B0H1WB5NTJ</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2640068</t>
+          <t>2640146</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>AM-Tyulian-UK</t>
+          <t>AM-Yulu-UK</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -4546,10 +4546,10 @@
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.63</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -4560,17 +4560,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>B0H1CXXQRB</t>
+          <t>B0H1VZKQJY</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2640117</t>
+          <t>2640145</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>AM-Yulu-UK</t>
+          <t>AM-Liuhu-UK</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -4594,17 +4594,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>B0H14PQ1V2</t>
+          <t>B0GZNV9NWM</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2640116</t>
+          <t>2640109</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>AM-Tyulian-UK</t>
+          <t>AM-Yulu-UK</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -4617,7 +4617,7 @@
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -4628,17 +4628,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>B0H2DMXMFC</t>
+          <t>B0H14PQ1V2</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2640171</t>
+          <t>2640116</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>AM-Yulu-UK</t>
+          <t>AM-Tyulian-UK</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -4662,17 +4662,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>B0H1M7DDVW</t>
+          <t>B0H35H5722</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2640116</t>
+          <t>2640217</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>AM-Tyulian-UK</t>
+          <t>AM-Yulu-UK</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -4685,7 +4685,7 @@
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -4696,17 +4696,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>B0H1BZ4CKG</t>
+          <t>B0H1CPTLDT</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2640139</t>
+          <t>2640131</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>AM-Tyulian-UK</t>
+          <t>AM-Yulu-UK</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -4719,7 +4719,7 @@
         <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -4730,17 +4730,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>B0H1W6487R</t>
+          <t>B0H1W8LNGT</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2640142</t>
+          <t>2640144</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>AM-Liuhu-UK</t>
+          <t>AM-shangchi-UK</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -4764,17 +4764,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>B0GZNMVRDT</t>
+          <t>B0H2DL1GKC</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2640102</t>
+          <t>2640168</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>AM-Yulu-UK</t>
+          <t>AM-Yujinbing-UK</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -4787,7 +4787,7 @@
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -4798,46 +4798,46 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>B0H1WWHWMH</t>
+          <t>B0GQY2XY86</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2640143</t>
+          <t>2640044</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>AM-Tyulian-UK</t>
+          <t>AM-Pyongqian-UK</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E46" t="n">
-        <v>0</v>
+        <v>98.89</v>
       </c>
       <c r="F46" t="n">
-        <v>0</v>
+        <v>5.56</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>欧洲精铺2025</t>
+          <t>欧洲精铺2025,欧洲精铺2025非标品</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>B0H2Z8PXZY</t>
+          <t>B0H2DMXMFC</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2640211</t>
+          <t>2640171</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -4866,12 +4866,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>B0GZNM54XT</t>
+          <t>B0GZNMVRDT</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2640107</t>
+          <t>2640102</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -4889,7 +4889,7 @@
         <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -4900,17 +4900,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>B0H14K2HHF</t>
+          <t>B0H35FT9Z7</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2640123</t>
+          <t>2640219</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>AM-Tyulian-UK</t>
+          <t>AM-Yulu-UK</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -4923,7 +4923,7 @@
         <v>0</v>
       </c>
       <c r="G49" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -4934,17 +4934,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>B0H2Y1QLG1</t>
+          <t>B0H1CS37WM</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2640194</t>
+          <t>2640128</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>AM-Tyulian-UK</t>
+          <t>AM-Yulu-UK</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -4957,7 +4957,7 @@
         <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -4968,17 +4968,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>B0H2YXWLJ7</t>
+          <t>B0H393GMYV</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2640190</t>
+          <t>2640224</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>AM-Yulu-UK</t>
+          <t>AM-Tyulian-DE</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -5002,17 +5002,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>B0H338VX3P</t>
+          <t>B0H2YTV3BQ</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2640214</t>
+          <t>2640189</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>AM-Tyulian-DE</t>
+          <t>AM-Yulu-UK</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -5036,17 +5036,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>B0H1WHLRJN</t>
+          <t>B0GZMHDZ7F</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2640151</t>
+          <t>2640106</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>AM-shangchi-UK</t>
+          <t>AM-Tyulian-DE</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -5056,10 +5056,10 @@
         <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>0</v>
+        <v>-0.17</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -5070,12 +5070,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>B0H11M6BHL</t>
+          <t>B0H2DJKK31</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2640127</t>
+          <t>2640167</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -5104,17 +5104,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>B0H24VSSGX</t>
+          <t>B0GZNS6RBN</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2640158</t>
+          <t>2640100</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>AM-Tyulian-DE</t>
+          <t>AM-Yulu-UK</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -5127,7 +5127,7 @@
         <v>0</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -5172,17 +5172,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>B0H2YB4CYH</t>
+          <t>B0H396CFPS</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2640212</t>
+          <t>2640232</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>AM-Tyulian-UK</t>
+          <t>AM-Tyulian-DE</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -5206,51 +5206,51 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>B0GQY2XY86</t>
+          <t>B0H2DQ4FQB</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2640044</t>
+          <t>2640172</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>AM-Pyongqian-UK</t>
+          <t>AM-Yujinbing-UK</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E58" t="n">
-        <v>98.89</v>
+        <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>5.56</v>
+        <v>0</v>
       </c>
       <c r="G58" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>欧洲精铺2025,欧洲精铺2025非标品</t>
+          <t>欧洲精铺2025</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>B0H1CS37WM</t>
+          <t>B0H33DBPRM</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2640128</t>
+          <t>2640178</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>AM-Yulu-UK</t>
+          <t>AM-Liuhu-UK</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -5263,7 +5263,7 @@
         <v>0</v>
       </c>
       <c r="G59" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
@@ -5274,12 +5274,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>B0H2YCT7QJ</t>
+          <t>B0H1WWHWMH</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2640183</t>
+          <t>2640143</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -5308,17 +5308,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>B0H1VZKQJY</t>
+          <t>B0H338VX3P</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2640145</t>
+          <t>2640214</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>AM-Liuhu-UK</t>
+          <t>AM-Tyulian-DE</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -5342,12 +5342,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>B0H1WV18XP</t>
+          <t>B0H35ZJ6VS</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2640152</t>
+          <t>2640213</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -5376,17 +5376,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>B0H2V9HTQP</t>
+          <t>B0H2YB4CYH</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2640196</t>
+          <t>2640212</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>AM-shangchi-UK</t>
+          <t>AM-Tyulian-UK</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -5410,17 +5410,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>B0H3BCPZGV</t>
+          <t>B0H2YGWGW5</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2640221</t>
+          <t>2640207</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>AM-Yujinbing-UK</t>
+          <t>AM-Tyulian-UK</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -5444,17 +5444,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>B0H35H5722</t>
+          <t>B0H1GLLCFJ</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2640217</t>
+          <t>2640133</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>AM-Yulu-UK</t>
+          <t>AM-Liuhu-UK</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -5478,17 +5478,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>B0H393GMYV</t>
+          <t>B0H2YJKM8P</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2640224</t>
+          <t>2640205</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>AM-Tyulian-DE</t>
+          <t>AM-Tyulian-UK</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -5512,17 +5512,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>B0H39LYWTC</t>
+          <t>B0H2YXWLJ7</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2640222</t>
+          <t>2640190</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>AM-Yujinbing-UK</t>
+          <t>AM-Yulu-UK</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -5546,12 +5546,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>B0GZNMPNPV</t>
+          <t>B0H2Z8PXZY</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2640101</t>
+          <t>2640211</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -5569,7 +5569,7 @@
         <v>0</v>
       </c>
       <c r="G68" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -5580,12 +5580,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>B0H35ZJ6VS</t>
+          <t>B0H2YCT7QJ</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2640213</t>
+          <t>2640183</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -5614,17 +5614,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>B0H1CPTLDT</t>
+          <t>B0H339HV8D</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2640131</t>
+          <t>2640217</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>AM-Yulu-UK</t>
+          <t>AM-Tyulian-DE</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -5637,7 +5637,7 @@
         <v>0</v>
       </c>
       <c r="G70" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -5648,17 +5648,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>B0H2YW1PZB</t>
+          <t>B0H1WV18XP</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2640181</t>
+          <t>2640152</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>AM-Yulu-UK</t>
+          <t>AM-Tyulian-UK</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -5682,17 +5682,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>B0H396CFPS</t>
+          <t>B0H39LYWTC</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2640232</t>
+          <t>2640222</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>AM-Tyulian-DE</t>
+          <t>AM-Yujinbing-UK</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -5716,17 +5716,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>B0H1CRQG45</t>
+          <t>B0H1BZ4CKG</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2640131</t>
+          <t>2640139</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>AM-Tyulian-DE</t>
+          <t>AM-Tyulian-UK</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -5739,7 +5739,7 @@
         <v>0</v>
       </c>
       <c r="G73" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
@@ -5750,17 +5750,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>B0GZNV9NWM</t>
+          <t>B0H2VTJZVG</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2640109</t>
+          <t>2640198</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>AM-Yulu-UK</t>
+          <t>AM-Yehao-UK</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -5773,7 +5773,7 @@
         <v>0</v>
       </c>
       <c r="G74" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
@@ -5784,17 +5784,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>B0H1W8LNGT</t>
+          <t>B0H33TQDHQ</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2640144</t>
+          <t>2640208</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>AM-shangchi-UK</t>
+          <t>AM-Liuhu-UK</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -5818,17 +5818,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>B0H339HV8D</t>
+          <t>B0H1M7DDVW</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2640217</t>
+          <t>2640116</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>AM-Tyulian-DE</t>
+          <t>AM-Tyulian-UK</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -5841,7 +5841,7 @@
         <v>0</v>
       </c>
       <c r="G76" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
@@ -5908,17 +5908,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>B0H3KKRR1S</t>
+          <t>B0H3LCMKHM</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2640229</t>
+          <t>2640226</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>AM-Yulu-UK</t>
+          <t>AM-Tyulian-UK</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -5942,17 +5942,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>B0H3LCMKHM</t>
+          <t>B0H3KQG6XL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2640226</t>
+          <t>2640227</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>AM-Tyulian-UK</t>
+          <t>AM-Yulu-UK</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -5976,17 +5976,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>B0H3V8NYWJ</t>
+          <t>B0H3KKRR1S</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2640245</t>
+          <t>2640229</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AM-Tyulian-DE</t>
+          <t>AM-Yulu-UK</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -6010,17 +6010,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>B0H3KQG6XL</t>
+          <t>B0H3V8NYWJ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2640227</t>
+          <t>2640245</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AM-Yulu-UK</t>
+          <t>AM-Tyulian-DE</t>
         </is>
       </c>
       <c r="D5" t="n">
